--- a/Methodology/RNN/03-PWM-X/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/RNN/03-PWM-X/Ts-03/Resumo_Estatisticas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Todos_Modelos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top_10_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Melhor_Modelo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +528,7 @@
         <v>3.421830345965173</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2222393650038619</v>
+        <v>0.2222393650038618</v>
       </c>
       <c r="F4" t="n">
         <v>0.3272061299913059</v>
@@ -569,7 +570,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.3118022592538354</v>
+        <v>-0.3118022592538353</v>
       </c>
       <c r="D6" t="n">
         <v>1.878494002674338</v>
@@ -593,13 +594,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-4.130976374250271</v>
+        <v>-4.13097637425027</v>
       </c>
       <c r="D7" t="n">
         <v>5.424859005246669</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4720722710938974</v>
+        <v>0.4720722710938973</v>
       </c>
       <c r="F7" t="n">
         <v>0.4991107586896996</v>
@@ -783,16 +784,230 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1.712456480658863</v>
+        <v>0.1731141552912583</v>
       </c>
       <c r="D7" t="n">
-        <v>4.117975553489836</v>
+        <v>0.2288628558647167</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2495578614421296</v>
+        <v>0.07607711479749091</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3788717643684623</v>
+        <v>0.02105638386473348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neurons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Best_R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_4_0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[8, 4]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9804187802566534</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_8_2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[16, 8]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9908274588503753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_16_3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[32, 16]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9003962983739532</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_32_3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[64, 32]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9847074070296642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_64_0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9929727168976836</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>model_128_2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[128]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6419393096761888</v>
       </c>
     </row>
   </sheetData>
